--- a/outputs/reports/gradient_boosting_v1/evaluation.xlsx
+++ b/outputs/reports/gradient_boosting_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9703149417843416</v>
+        <v>0.9658117369886485</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09277899343544858</v>
+        <v>0.07306756899651053</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8565656565656565</v>
+        <v>0.7997685185185185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1674234945705824</v>
+        <v>0.1339017537060362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9707126862245078</v>
+        <v>0.9663622409823485</v>
       </c>
       <c r="G2" t="n">
-        <v>137417</v>
+        <v>251834</v>
       </c>
       <c r="H2" t="n">
-        <v>4146</v>
+        <v>8766</v>
       </c>
       <c r="I2" t="n">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="J2" t="n">
-        <v>424</v>
+        <v>691</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9626496166142824</v>
+        <v>0.9442600409311844</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7145772105801805</v>
+        <v>0.4724960271000102</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C2" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2871217452498241</v>
+        <v>0.2332695984703633</v>
       </c>
       <c r="E2" t="n">
-        <v>82.39988057919093</v>
+        <v>70.59213228524892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8242424242424242</v>
+        <v>0.7060185185185185</v>
       </c>
       <c r="G2" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06124172884696607</v>
+        <v>0.05415328132170721</v>
       </c>
       <c r="I2" t="n">
-        <v>17.5755101344289</v>
+        <v>16.38788605034589</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.8194444444444444</v>
       </c>
       <c r="K2" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03188793467548923</v>
+        <v>0.02830152598768501</v>
       </c>
       <c r="M2" t="n">
-        <v>9.151386311375047</v>
+        <v>8.5646182764399</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9151515151515152</v>
+        <v>0.8564814814814815</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88405</v>
+        <v>154025</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002149199705898988</v>
+        <v>0.0002726830060055186</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22820</v>
+        <v>44133</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005258545135845749</v>
+        <v>0.0008610336936079577</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13217</v>
+        <v>26787</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000529620942725278</v>
+        <v>0.001119946242580356</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8177</v>
+        <v>16979</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001712119359178183</v>
+        <v>0.001649095942046057</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4851</v>
+        <v>10052</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003710575139146568</v>
+        <v>0.003481894150417827</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2650</v>
+        <v>5512</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004528301886792453</v>
+        <v>0.01070391872278665</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1132</v>
+        <v>2380</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01943462897526502</v>
+        <v>0.0273109243697479</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>387</v>
+        <v>847</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1343669250645995</v>
+        <v>0.1003541912632822</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="C10" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6815642458100558</v>
+        <v>0.5567010309278351</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>240</v>
+        <v>458</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>320</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9041666666666667</v>
+        <v>0.6986899563318777</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/gradient_boosting_v1/evaluation.xlsx
+++ b/outputs/reports/gradient_boosting_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9658117369886485</v>
+        <v>0.9863537618945629</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07306756899651053</v>
+        <v>0.1816904706157808</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7997685185185185</v>
+        <v>0.9140164899882215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1339017537060362</v>
+        <v>0.303125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9663622409823485</v>
+        <v>0.9865894135026764</v>
       </c>
       <c r="G2" t="n">
-        <v>251834</v>
+        <v>257120</v>
       </c>
       <c r="H2" t="n">
-        <v>8766</v>
+        <v>3495</v>
       </c>
       <c r="I2" t="n">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="J2" t="n">
-        <v>691</v>
+        <v>776</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9442600409311844</v>
+        <v>0.9835206145868565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4724960271000102</v>
+        <v>0.7524558562078887</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
         <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2332695984703633</v>
+        <v>0.2902485659655832</v>
       </c>
       <c r="E2" t="n">
-        <v>70.59213228524892</v>
+        <v>89.38698592653149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7060185185185185</v>
+        <v>0.8939929328621908</v>
       </c>
       <c r="G2" t="n">
         <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05415328132170721</v>
+        <v>0.06096068532966192</v>
       </c>
       <c r="I2" t="n">
-        <v>16.38788605034589</v>
+        <v>18.77388059956976</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8194444444444444</v>
+        <v>0.9387514723203769</v>
       </c>
       <c r="K2" t="n">
         <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02830152598768501</v>
+        <v>0.03116992389184228</v>
       </c>
       <c r="M2" t="n">
-        <v>8.5646182764399</v>
+        <v>9.599308575331742</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8564814814814815</v>
+        <v>0.9599528857479388</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>154025</v>
+        <v>201296</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002726830060055186</v>
+        <v>0.0001142595978062157</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44133</v>
+        <v>31071</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008610336936079577</v>
+        <v>0.0003218435196807312</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26787</v>
+        <v>14064</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001119946242580356</v>
+        <v>0.001137656427758817</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16979</v>
+        <v>7185</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001649095942046057</v>
+        <v>0.001530967292971468</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10052</v>
+        <v>3569</v>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003481894150417827</v>
+        <v>0.003642476884281311</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5512</v>
+        <v>1826</v>
       </c>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01070391872278665</v>
+        <v>0.0104052573932092</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2380</v>
+        <v>1038</v>
       </c>
       <c r="C8" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0273109243697479</v>
+        <v>0.03275529865125241</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>847</v>
+        <v>475</v>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1003541912632822</v>
+        <v>0.1031578947368421</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>291</v>
+        <v>241</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5567010309278351</v>
+        <v>0.4107883817427386</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>458</v>
+        <v>699</v>
       </c>
       <c r="C11" t="n">
-        <v>320</v>
+        <v>575</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6986899563318777</v>
+        <v>0.8226037195994278</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/gradient_boosting_v1/evaluation.xlsx
+++ b/outputs/reports/gradient_boosting_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9863537618945629</v>
+        <v>0.995746887966805</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1816904706157808</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9140164899882215</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.303125</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9865894135026764</v>
+        <v>0.9986978488462941</v>
       </c>
       <c r="G2" t="n">
-        <v>257120</v>
+        <v>38348</v>
       </c>
       <c r="H2" t="n">
-        <v>3495</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="J2" t="n">
-        <v>776</v>
+        <v>48</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9835206145868565</v>
+        <v>0.873887384180889</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7524558562078887</v>
+        <v>0.3178885794856454</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2902485659655832</v>
+        <v>0.1658031088082902</v>
       </c>
       <c r="E2" t="n">
-        <v>89.38698592653149</v>
+        <v>39.46523380029425</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8939929328621908</v>
+        <v>0.3950617283950617</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06096068532966192</v>
+        <v>0.04719917012448133</v>
       </c>
       <c r="I2" t="n">
-        <v>18.77388059956976</v>
+        <v>11.23456790123457</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9387514723203769</v>
+        <v>0.5617283950617284</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03116992389184228</v>
+        <v>0.02697095435684647</v>
       </c>
       <c r="M2" t="n">
-        <v>9.599308575331742</v>
+        <v>6.419753086419754</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9599528857479388</v>
+        <v>0.6419753086419753</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>201296</v>
+        <v>37463</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001142595978062157</v>
+        <v>0.002242212316151937</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31071</v>
+        <v>650</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003218435196807312</v>
+        <v>0.02</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14064</v>
+        <v>211</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001137656427758817</v>
+        <v>0.03791469194312796</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7185</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001530967292971468</v>
+        <v>0.0641025641025641</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3569</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003642476884281311</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1826</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0104052573932092</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1038</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03275529865125241</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>475</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1031578947368421</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4107883817427386</v>
+        <v>0.9</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>699</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>575</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8226037195994278</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
